--- a/dados/excel/indice.xlsx
+++ b/dados/excel/indice.xlsx
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 24/09/2026 19:18 · 48 arquivos com sucesso</t>
+          <t>Gerado em 10/10/2026 14:55 · 48 arquivos com sucesso</t>
         </is>
       </c>
     </row>
@@ -537,7 +537,7 @@
         <v>269</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>4</v>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="D6" s="5" t="n">
         <v>8</v>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>4960</v>
+        <v>5063</v>
       </c>
       <c r="D7" s="5" t="n">
         <v>8</v>
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1956</v>
+        <v>1995</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>7</v>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D9" s="5" t="n">
         <v>11</v>
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>1332</v>
+        <v>1360</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>4</v>
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>7</v>
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D13" s="5" t="n">
         <v>6</v>
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" s="5" t="n">
         <v>7</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1332</v>
+        <v>1360</v>
       </c>
       <c r="D15" s="5" t="n">
         <v>8</v>
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>7</v>
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D23" s="5" t="n">
         <v>8</v>
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D24" s="5" t="n">
         <v>4</v>
@@ -1080,7 +1080,7 @@
         </is>
       </c>
       <c r="C26" s="5" t="n">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D26" s="5" t="n">
         <v>7</v>
@@ -1288,7 +1288,7 @@
         </is>
       </c>
       <c r="C34" s="5" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D34" s="5" t="n">
         <v>6</v>
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="C36" s="5" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D36" s="5" t="n">
         <v>7</v>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D39" s="5" t="n">
         <v>6</v>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="C42" s="5" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="D42" s="5" t="n">
         <v>5</v>
@@ -1522,7 +1522,7 @@
         </is>
       </c>
       <c r="C43" s="5" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D43" s="5" t="n">
         <v>7</v>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="C44" s="5" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D44" s="5" t="n">
         <v>5</v>
@@ -1652,7 +1652,7 @@
         </is>
       </c>
       <c r="C48" s="5" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D48" s="5" t="n">
         <v>5</v>
@@ -1704,10 +1704,10 @@
         </is>
       </c>
       <c r="C50" s="5" t="n">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E50" s="5" t="n">
         <v>3</v>
@@ -1730,7 +1730,7 @@
         </is>
       </c>
       <c r="C51" s="5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D51" s="5" t="n">
         <v>5</v>
@@ -1759,7 +1759,7 @@
         <v>20</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E52" s="5" t="n">
         <v>2</v>
